--- a/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
@@ -469,10 +469,10 @@
         <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Everette</v>
+        <v>Garrison</v>
       </c>
       <c r="C2" t="str">
-        <v>Schaden</v>
+        <v>Rau-Schumm</v>
       </c>
       <c r="D2" t="str">
         <v>13332</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>6533988896</v>
+        <v>1403505871</v>
       </c>
       <c r="N2" t="str">
-        <v>everette@yopmail.com</v>
+        <v>garrison@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>

--- a/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
@@ -469,10 +469,10 @@
         <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Garrison</v>
+        <v>Crawford</v>
       </c>
       <c r="C2" t="str">
-        <v>Rau-Schumm</v>
+        <v>Wunsch</v>
       </c>
       <c r="D2" t="str">
         <v>13332</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>1403505871</v>
+        <v>4251148313</v>
       </c>
       <c r="N2" t="str">
-        <v>garrison@yopmail.com</v>
+        <v>crawford@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>

--- a/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Telecaller</v>
+        <v>FOS</v>
       </c>
       <c r="B2" t="str">
-        <v>Crawford</v>
+        <v>Pascale</v>
       </c>
       <c r="C2" t="str">
-        <v>Wunsch</v>
+        <v>Emard</v>
       </c>
       <c r="D2" t="str">
         <v>13332</v>
@@ -481,16 +481,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>435454</v>
+        <v>435ab#@#%4</v>
       </c>
       <c r="G2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>23577359447</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>Agency Frontend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>4251148313</v>
+        <v>5782927479</v>
       </c>
       <c r="N2" t="str">
-        <v>crawford@yopmail.com</v>
+        <v>pascale@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>re35sr</v>
+        <v>resr</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FOS</v>
+        <v>Telecaller</v>
       </c>
       <c r="B2" t="str">
-        <v>Pascale</v>
+        <v>Pierre</v>
       </c>
       <c r="C2" t="str">
-        <v>Emard</v>
+        <v>Spinka</v>
       </c>
       <c r="D2" t="str">
         <v>13332</v>
@@ -481,16 +481,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>435ab#@#%4</v>
+        <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>10-10-2020</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>23577359447</v>
       </c>
       <c r="J2" t="str">
         <v>Agency Frontend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>5782927479</v>
+        <v>9596347344</v>
       </c>
       <c r="N2" t="str">
-        <v>pascale@yopmail.com</v>
+        <v>pierre@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>resr</v>
+        <v>re35sr</v>
       </c>
     </row>
   </sheetData>

--- a/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
+++ b/March_Release_SCB_UAT/Cypress/fixtures/AgentTemplate.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Telecaller</v>
+        <v>FOS</v>
       </c>
       <c r="B2" t="str">
-        <v>Pierre</v>
+        <v>Katrine</v>
       </c>
       <c r="C2" t="str">
-        <v>Spinka</v>
+        <v>Gorczany</v>
       </c>
       <c r="D2" t="str">
         <v>13332</v>
@@ -484,13 +484,13 @@
         <v>435454</v>
       </c>
       <c r="G2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>10-10-2020</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>23577359447</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>Agency Frontend</v>
@@ -502,10 +502,10 @@
         <v>18-10-1979</v>
       </c>
       <c r="M2" t="str">
-        <v>9596347344</v>
+        <v>4663388728</v>
       </c>
       <c r="N2" t="str">
-        <v>pierre@yopmail.com</v>
+        <v>katrine@yopmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>yop</v>
@@ -526,7 +526,7 @@
         <v>10-10-2033</v>
       </c>
       <c r="U2" t="str">
-        <v>re35sr</v>
+        <v>resr</v>
       </c>
     </row>
   </sheetData>
